--- a/data/trending_integrated_20260922_15.xlsx
+++ b/data/trending_integrated_20260922_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F2" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52591170040</v>
+        <v>52594868240</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5476982409</v>
+        <v>5477057419</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,21 +751,21 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65500</v>
+        <v>65400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.24%</t>
+          <t>'+25.05%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G4" t="n">
         <v>166</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>178227083350</v>
+        <v>179514456100</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 뉴스 기반 상승 기대. 20일선 안착 여부 및 키 맞추기 가능성 언급.</t>
+          <t>브로드컴 투자 공급 계약 관련 호재와 함께 급등 기대감. 단기 고점 매도 의견도 일부 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['공급계약', '20일선', '키맞추기']</t>
+          <t>['브로드컴', '공급 계약', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13550</v>
+        <v>13510</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.85%</t>
+          <t>'+21.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="F5" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>595</v>
+        <v>601</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>275578979330</v>
+        <v>280372028480</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>역대급 거래량과 함께 매집 움직임이 포착되며, 단기 상승 기대감과 함께 장기적인 관점에서 큰 상승 가능성에 대한 전망이 제기됨. 일부 매도 물량에 대한 의문 제기.</t>
+          <t>상한가 기대감과 함께 거래량 증가 및 물량 확보 언급. 단기 하락 가능성 및 사기꾼 언급도 존재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '매집', '상승']</t>
+          <t>['거래량', '상한가', '수급']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>112200</v>
+        <v>111800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+10.11%</t>
+          <t>'+9.72%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G6" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>316561717400</v>
+        <v>319316614550</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1038,13 +1038,13 @@
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="F7" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="H7" t="n">
         <v>1.2</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>100084507600</v>
+        <v>104601563225</v>
       </c>
       <c r="P7" t="n">
         <v>24100</v>
@@ -1130,16 +1130,16 @@
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F8" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G8" t="n">
-        <v>444</v>
+        <v>468</v>
       </c>
       <c r="H8" t="n">
-        <v>52.6</v>
+        <v>52.65</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>190011565125</v>
+        <v>195895520225</v>
       </c>
       <c r="P8" t="n">
         <v>31400</v>
@@ -1222,13 +1222,13 @@
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="F9" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G9" t="n">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="H9" t="n">
         <v>11.3</v>
@@ -1254,7 +1254,7 @@
         <v>11.92</v>
       </c>
       <c r="O9" t="n">
-        <v>278121509475</v>
+        <v>280913335475</v>
       </c>
       <c r="P9" t="n">
         <v>75900</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18890</v>
+        <v>18810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.28%</t>
+          <t>'+2.84%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>787</v>
+        <v>809</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>159967900870</v>
+        <v>161769512015</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 세력과의 싸움 속에서 2만 돌파 및 상한가 기대감 형성. 감사원 신고 완료 및 공매도 장부 조작 의혹 제기.</t>
+          <t>감사원 신고 및 공매도 관련 의혹 제기로 주가 부양 기대감 형성. 뉴스 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '상한가', '감사원']</t>
+          <t>['공매도', '감사원', '뉴스']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6470</v>
+        <v>6450</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.54%</t>
+          <t>'+2.22%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="F11" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G11" t="n">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="H11" t="n">
         <v>4.86</v>
@@ -1438,7 +1438,7 @@
         <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>55072077565</v>
+        <v>55288460405</v>
       </c>
       <c r="P11" t="n">
         <v>11760</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6000</v>
+        <v>5980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.39%</t>
+          <t>'+2.05%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.19</v>
       </c>
       <c r="E12" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
         <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0.19</v>
       </c>
       <c r="O12" t="n">
-        <v>69430546720</v>
+        <v>69621245870</v>
       </c>
       <c r="P12" t="n">
         <v>13140</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13260</v>
+        <v>13220</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.31%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G13" t="n">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>23504361770</v>
+        <v>23691914280</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1671,11 +1671,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>212000</v>
+        <v>211500</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+1.92%</t>
+          <t>'+1.68%</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1685,10 +1685,10 @@
         <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H14" t="n">
         <v>75.5</v>
@@ -1714,7 +1714,7 @@
         <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>940518386750</v>
+        <v>971155794000</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86600</v>
+        <v>277750</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.52%</t>
+          <t>'+1.37%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="E15" t="n">
-        <v>431</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>223</v>
+        <v>478</v>
       </c>
       <c r="G15" t="n">
-        <v>1572</v>
+        <v>1812</v>
       </c>
       <c r="H15" t="n">
-        <v>23.05</v>
+        <v>46.56</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>85300</v>
+        <v>274000</v>
       </c>
       <c r="K15" t="n">
-        <v>87000</v>
+        <v>283000</v>
       </c>
       <c r="L15" t="n">
-        <v>88100</v>
+        <v>283500</v>
       </c>
       <c r="M15" t="n">
-        <v>85200</v>
+        <v>274500</v>
       </c>
       <c r="N15" t="n">
-        <v>23.12</v>
+        <v>46.46</v>
       </c>
       <c r="O15" t="n">
-        <v>231255781550</v>
+        <v>4269535192500</v>
       </c>
       <c r="P15" t="n">
-        <v>139200</v>
+        <v>374500</v>
       </c>
       <c r="Q15" t="n">
-        <v>57000</v>
+        <v>81100</v>
       </c>
       <c r="R15" t="n">
-        <v>-253000</v>
+        <v>749000</v>
       </c>
       <c r="S15" t="n">
-        <v>7000</v>
+        <v>262000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>대미 투자(SMR, 가스터빈) 관련 공급 계약 체결 및 사업 추진 확정. 긍정적 뉴스에 힘입어 주가 상승 기대감이 매우 높으며, 공매도 세력에 대한 비판 의견도 존재.</t>
+          <t>정치 관련 논쟁과 함께 주가 상승 및 배당 기대감 언급. 공매도와 관련된 내용도 일부 포함.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '대미투자', '공급계약']</t>
+          <t>['배당', '공매도', '주가']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13740</v>
+        <v>13710</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.48%</t>
+          <t>'+1.26%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1872,7 +1872,7 @@
         <v>48</v>
       </c>
       <c r="G16" t="n">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
         <v>3.34</v>
@@ -1898,7 +1898,7 @@
         <v>3.68</v>
       </c>
       <c r="O16" t="n">
-        <v>99857001070</v>
+        <v>100499059010</v>
       </c>
       <c r="P16" t="n">
         <v>20300</v>
@@ -1943,31 +1943,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>277500</v>
+        <v>86350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>800</v>
+        <v>437</v>
       </c>
       <c r="F17" t="n">
-        <v>473</v>
+        <v>225</v>
       </c>
       <c r="G17" t="n">
-        <v>1774</v>
+        <v>1597</v>
       </c>
       <c r="H17" t="n">
-        <v>46.56</v>
+        <v>23.05</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,51 +1975,51 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>274000</v>
+        <v>85300</v>
       </c>
       <c r="K17" t="n">
-        <v>283000</v>
+        <v>87000</v>
       </c>
       <c r="L17" t="n">
-        <v>283500</v>
+        <v>88100</v>
       </c>
       <c r="M17" t="n">
-        <v>274500</v>
+        <v>85200</v>
       </c>
       <c r="N17" t="n">
-        <v>46.46</v>
+        <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>4188844944750</v>
+        <v>236160000900</v>
       </c>
       <c r="P17" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>81100</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>749000</v>
+        <v>-253000</v>
       </c>
       <c r="S17" t="n">
-        <v>262000</v>
+        <v>7000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>전반적으로 부정적 의견과 함께 정치적 논쟁이 혼재. 단기적인 주가 상승 기대 언급 있으나, 장기 투자에 대한 회의적인 시각 존재.</t>
+          <t>대미 투자(SMR, 가스터빈) 관련 공급 계약 체결 및 사업 추진 확정. 긍정적 뉴스에 힘입어 주가 상승 기대감이 매우 높으며, 공매도 세력에 대한 비판 의견도 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['배당', '실적', '투자']</t>
+          <t>['SMR', '대미투자', '공급계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>322500</v>
+        <v>321500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.26%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="F18" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="H18" t="n">
         <v>3.22</v>
@@ -2082,7 +2082,7 @@
         <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>130209786750</v>
+        <v>131140932250</v>
       </c>
       <c r="P18" t="n">
         <v>635000</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17830</v>
+        <v>17790</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.62%</t>
+          <t>'+0.40%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F19" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="G19" t="n">
-        <v>869</v>
+        <v>884</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>170753303135</v>
+        <v>173027542165</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13480</v>
+        <v>13410</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.60%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.48</v>
       </c>
       <c r="E20" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F20" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G20" t="n">
-        <v>589</v>
+        <v>621</v>
       </c>
       <c r="H20" t="n">
         <v>5.02</v>
@@ -2266,7 +2266,7 @@
         <v>5.5</v>
       </c>
       <c r="O20" t="n">
-        <v>69681114460</v>
+        <v>70375345955</v>
       </c>
       <c r="P20" t="n">
         <v>30200</v>
@@ -2326,13 +2326,13 @@
         <v>1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="H21" t="n">
         <v>9.609999999999999</v>
@@ -2358,7 +2358,7 @@
         <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>150282228400</v>
+        <v>152116521240</v>
       </c>
       <c r="P21" t="n">
         <v>11640</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8460</v>
+        <v>8450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.70%</t>
+          <t>'-0.82%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>21979713780</v>
+        <v>22468855745</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 부진에 대한 답답함과 기대감 혼재. ADR 계산법 및 기관 순매수 동향 언급. 최악의 회사라는 평가도.</t>
+          <t>주가 상승 기대와 함께 기관 순매수 및 ADR 계산 언급. 회사 실적 및 재무 구조에 대한 부정적 시각도 존재.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가', 'ADR', '기관']</t>
+          <t>['기관', 'ADR', '재무']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1854000</v>
+        <v>1847000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-0.75%</t>
+          <t>'-1.12%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="G23" t="n">
-        <v>1395</v>
+        <v>1454</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>5071384395000</v>
+        <v>5190243222500</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>연기금 및 외인의 매도세에 대한 강한 불만 표출. 메모리 반도체 시장 상황에도 불구하고 주가 하락에 대한 실망감과 향후 폭락 가능성에 대한 우려가 높음.</t>
+          <t>주가 하락에 대한 불만과 연기금, 레버리지에 대한 비판. 향후 폭락 가능성 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['연기금', '반도체', '하락']</t>
+          <t>['하락', '연기금', '레버리지']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2608,7 +2608,7 @@
         <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>110332947525</v>
+        <v>111139890450</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2679,184 +2679,184 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3765</v>
+        <v>10200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.15%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>135</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>347</v>
+        <v>273</v>
       </c>
       <c r="H25" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J25" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K25" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L25" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M25" t="n">
-        <v>3710</v>
+        <v>10060</v>
       </c>
       <c r="N25" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>13776561175</v>
+        <v>42501705055</v>
       </c>
       <c r="P25" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q25" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R25" t="n">
-        <v>-78000</v>
+        <v>-11000</v>
       </c>
       <c r="S25" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>급락 후 반등 기대감과 폭락 우려 공존. 코인주 텐베거 가능성 및 차트 분석 언급. 선수 퇴장 및 개미 몰살 중.</t>
+          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>['코인주', '차트', '급락']</t>
+          <t>['투자경고', '단주치기', '주가']</t>
         </is>
       </c>
       <c r="X25" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>017900</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>10230</v>
+        <v>3725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.50%</t>
+          <t>'-8.14%</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>93</v>
+        <v>139</v>
       </c>
       <c r="F26" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="G26" t="n">
-        <v>268</v>
+        <v>346</v>
       </c>
       <c r="H26" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K26" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L26" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M26" t="n">
-        <v>10060</v>
+        <v>3710</v>
       </c>
       <c r="N26" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>42137663070</v>
+        <v>14169923735</v>
       </c>
       <c r="P26" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q26" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R26" t="n">
-        <v>-11000</v>
+        <v>-78000</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 및 단주치기 등 거래 행태에 대한 부정적 인식. 주가 하락 우려.</t>
+          <t>급락 후 반등 기대감과 폭락 우려 공존. 코인주 텐베거 가능성 및 차트 분석 언급. 선수 퇴장 및 개미 몰살 중.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>['투자경고', '단주치기', '주가']</t>
+          <t>['코인주', '차트', '급락']</t>
         </is>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_15.xlsx
+++ b/data/trending_integrated_20260922_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F2" t="n">
         <v>96</v>
       </c>
       <c r="G2" t="n">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52594868240</v>
+        <v>52617034890</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 소식과 함께 기술력에 대한 높은 평가. 퓨리오사 AI 관련주로 부각되며, 로봇팔 작업 속도 초가속 등 혁신적인 기술력으로 큰 폭의 상승이 전망됨.</t>
+          <t>노타의 국산 NPU 기반 휴머노이드 개발 착수 및 AI 반도체 기술력에 대한 높은 기대감.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', 'AI']</t>
+          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5477057419</v>
+        <v>5481667649</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65400</v>
+        <v>65900</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+25.05%</t>
+          <t>'+26.00%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F4" t="n">
         <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>179514456100</v>
+        <v>183021761250</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13510</v>
+        <v>13480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.49%</t>
+          <t>'+21.22%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F5" t="n">
         <v>120</v>
       </c>
       <c r="G5" t="n">
-        <v>601</v>
+        <v>621</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>280372028480</v>
+        <v>283953020475</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>상한가 기대감과 함께 거래량 증가 및 물량 확보 언급. 단기 하락 가능성 및 사기꾼 언급도 존재.</t>
+          <t>삼미금속의 단기 급등 후 변동성 및 투자자 간의 의견 대립.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '상한가', '수급']</t>
+          <t>['거래량', '변동성', '주주']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>111800</v>
+        <v>112300</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+9.72%</t>
+          <t>'+10.21%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>319316614550</v>
+        <v>321165327200</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23400</v>
+        <v>23600</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+8.84%</t>
+          <t>'+9.77%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="H7" t="n">
         <v>1.2</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>104601563225</v>
+        <v>107572549725</v>
       </c>
       <c r="P7" t="n">
         <v>24100</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>모더나, 머크 등 글로벌 제약사들의 임상 투자 소식과 함께 주가 상승 기대감이 높음. 기타법인 및 외국인의 매수세 유입으로 신고가 돌파 및 향후 3만 원 돌파 가능성에 대한 전망이 나옴.</t>
+          <t>인제니아테라퓨틱스의 임상 3상 투자 및 바이오 의약품 시장 동향과 연계된 기대감.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상', '신약', '상승']</t>
+          <t>['임상 3상', '바이오', '신고가']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31300</v>
+        <v>31350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.49%</t>
+          <t>'+8.67%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="F8" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>468</v>
+        <v>487</v>
       </c>
       <c r="H8" t="n">
-        <v>52.65</v>
+        <v>52.76</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>195895520225</v>
+        <v>203726382725</v>
       </c>
       <c r="P8" t="n">
         <v>31400</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31650</v>
+        <v>31600</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+6.57%</t>
+          <t>'+6.40%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>86</v>
       </c>
       <c r="G9" t="n">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="H9" t="n">
         <v>11.3</v>
@@ -1254,7 +1254,7 @@
         <v>11.92</v>
       </c>
       <c r="O9" t="n">
-        <v>280913335475</v>
+        <v>283246655725</v>
       </c>
       <c r="P9" t="n">
         <v>75900</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18810</v>
+        <v>18770</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.84%</t>
+          <t>'+2.62%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>161769512015</v>
+        <v>163198725870</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1391,70 +1391,70 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6450</v>
+        <v>13230</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+2.22%</t>
+          <t>'+2.08%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>204</v>
+        <v>410</v>
       </c>
       <c r="H11" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>6310</v>
+        <v>12960</v>
       </c>
       <c r="K11" t="n">
-        <v>6460</v>
+        <v>13500</v>
       </c>
       <c r="L11" t="n">
-        <v>7090</v>
+        <v>14190</v>
       </c>
       <c r="M11" t="n">
-        <v>6330</v>
+        <v>13100</v>
       </c>
       <c r="N11" t="n">
-        <v>4.95</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>55288460405</v>
+        <v>23887455180</v>
       </c>
       <c r="P11" t="n">
-        <v>11760</v>
+        <v>19380</v>
       </c>
       <c r="Q11" t="n">
-        <v>1620</v>
+        <v>3200</v>
       </c>
       <c r="R11" t="n">
-        <v>-112000</v>
+        <v>-49000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
         <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0.19</v>
       </c>
       <c r="O12" t="n">
-        <v>69621245870</v>
+        <v>69813403360</v>
       </c>
       <c r="P12" t="n">
         <v>13140</v>
@@ -1575,70 +1575,70 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13220</v>
+        <v>6420</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+1.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="F13" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="G13" t="n">
-        <v>412</v>
+        <v>210</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>4.86</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>6310</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>6460</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>7090</v>
       </c>
       <c r="M13" t="n">
-        <v>13100</v>
+        <v>6330</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="O13" t="n">
-        <v>23691914280</v>
+        <v>55534013060</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>11760</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>1620</v>
       </c>
       <c r="R13" t="n">
-        <v>-49000</v>
+        <v>-112000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
@@ -1647,11 +1647,11 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
@@ -1682,13 +1682,13 @@
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="F14" t="n">
         <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H14" t="n">
         <v>75.5</v>
@@ -1714,7 +1714,7 @@
         <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>971155794000</v>
+        <v>1008513451000</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1759,31 +1759,31 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>277750</v>
+        <v>86400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.37%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>444</v>
       </c>
       <c r="F15" t="n">
-        <v>478</v>
+        <v>229</v>
       </c>
       <c r="G15" t="n">
-        <v>1812</v>
+        <v>1635</v>
       </c>
       <c r="H15" t="n">
-        <v>46.56</v>
+        <v>23.05</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,51 +1791,51 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>274000</v>
+        <v>85300</v>
       </c>
       <c r="K15" t="n">
-        <v>283000</v>
+        <v>87000</v>
       </c>
       <c r="L15" t="n">
-        <v>283500</v>
+        <v>88100</v>
       </c>
       <c r="M15" t="n">
-        <v>274500</v>
+        <v>85200</v>
       </c>
       <c r="N15" t="n">
-        <v>46.46</v>
+        <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>4269535192500</v>
+        <v>239382549100</v>
       </c>
       <c r="P15" t="n">
-        <v>374500</v>
+        <v>139200</v>
       </c>
       <c r="Q15" t="n">
-        <v>81100</v>
+        <v>57000</v>
       </c>
       <c r="R15" t="n">
-        <v>749000</v>
+        <v>-253000</v>
       </c>
       <c r="S15" t="n">
-        <v>262000</v>
+        <v>7000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>정치 관련 논쟁과 함께 주가 상승 및 배당 기대감 언급. 공매도와 관련된 내용도 일부 포함.</t>
+          <t>두산에너빌리티의 미국 투자 확정 및 SMR 추진 관련 긍정적 전망과 공매도 관련 부정적 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['배당', '공매도', '주가']</t>
+          <t>['SMR', '미국 투자', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13710</v>
+        <v>277500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.26%</t>
+          <t>'+1.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.34</v>
+        <v>0.1</v>
       </c>
       <c r="E16" t="n">
-        <v>89</v>
+        <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>48</v>
+        <v>478</v>
       </c>
       <c r="G16" t="n">
-        <v>234</v>
+        <v>1938</v>
       </c>
       <c r="H16" t="n">
-        <v>3.34</v>
+        <v>46.56</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,91 +1883,91 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>13540</v>
+        <v>274000</v>
       </c>
       <c r="K16" t="n">
-        <v>13870</v>
+        <v>283000</v>
       </c>
       <c r="L16" t="n">
-        <v>14650</v>
+        <v>283500</v>
       </c>
       <c r="M16" t="n">
-        <v>13570</v>
+        <v>274500</v>
       </c>
       <c r="N16" t="n">
-        <v>3.68</v>
+        <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>100499059010</v>
+        <v>4366135550250</v>
       </c>
       <c r="P16" t="n">
-        <v>20300</v>
+        <v>374500</v>
       </c>
       <c r="Q16" t="n">
-        <v>2885</v>
+        <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>2000</v>
+        <v>749000</v>
       </c>
       <c r="S16" t="n">
-        <v>16000</v>
+        <v>262000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>정치적 언급과 함께 삼성전자 주가 반등 및 배당 관련 논쟁.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['배당', '정치', '주가']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86350</v>
+        <v>13660</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.34</v>
       </c>
       <c r="E17" t="n">
-        <v>437</v>
+        <v>90</v>
       </c>
       <c r="F17" t="n">
-        <v>225</v>
+        <v>48</v>
       </c>
       <c r="G17" t="n">
-        <v>1597</v>
+        <v>235</v>
       </c>
       <c r="H17" t="n">
-        <v>23.05</v>
+        <v>3.34</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,60 +1975,60 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85300</v>
+        <v>13540</v>
       </c>
       <c r="K17" t="n">
-        <v>87000</v>
+        <v>13870</v>
       </c>
       <c r="L17" t="n">
-        <v>88100</v>
+        <v>14650</v>
       </c>
       <c r="M17" t="n">
-        <v>85200</v>
+        <v>13570</v>
       </c>
       <c r="N17" t="n">
-        <v>23.12</v>
+        <v>3.68</v>
       </c>
       <c r="O17" t="n">
-        <v>236160000900</v>
+        <v>101319925950</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>20300</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>2885</v>
       </c>
       <c r="R17" t="n">
-        <v>-253000</v>
+        <v>2000</v>
       </c>
       <c r="S17" t="n">
-        <v>7000</v>
+        <v>16000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>대미 투자(SMR, 가스터빈) 관련 공급 계약 체결 및 사업 추진 확정. 긍정적 뉴스에 힘입어 주가 상승 기대감이 매우 높으며, 공매도 세력에 대한 비판 의견도 존재.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '대미투자', '공급계약']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321500</v>
+        <v>321000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.94%</t>
+          <t>'+0.78%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>-0.4</v>
       </c>
       <c r="E18" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F18" t="n">
         <v>83</v>
       </c>
       <c r="G18" t="n">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="H18" t="n">
         <v>3.22</v>
@@ -2082,7 +2082,7 @@
         <v>3.62</v>
       </c>
       <c r="O18" t="n">
-        <v>131140932250</v>
+        <v>132418395500</v>
       </c>
       <c r="P18" t="n">
         <v>635000</v>
@@ -2098,16 +2098,16 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>52주 신고가 돌파 및 40만원, 50만원 목표 제시. 구리 가격 상승 및 발전 프로젝트 테마 언급. 야수의 심장으로 덤빌 구간 진입.</t>
+          <t>가온전선의 52주 신고가 돌파 및 텍사스 발전 프로젝트 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['신고가', '테마주', '목표가']</t>
+          <t>['신고가', '구리', '프로젝트']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2127,31 +2127,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17790</v>
+        <v>10610</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.40%</t>
+          <t>'+0.57%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.68</v>
+        <v>1.01</v>
       </c>
       <c r="E19" t="n">
-        <v>205</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>112</v>
+        <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>884</v>
+        <v>209</v>
       </c>
       <c r="H19" t="n">
-        <v>6.22</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -2159,91 +2159,91 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17720</v>
+        <v>10550</v>
       </c>
       <c r="K19" t="n">
-        <v>18230</v>
+        <v>10730</v>
       </c>
       <c r="L19" t="n">
-        <v>18750</v>
+        <v>11160</v>
       </c>
       <c r="M19" t="n">
-        <v>17500</v>
+        <v>10300</v>
       </c>
       <c r="N19" t="n">
-        <v>7.9</v>
+        <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>173027542165</v>
+        <v>153589043530</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>11640</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>3735</v>
       </c>
       <c r="R19" t="n">
-        <v>-475000</v>
+        <v>326000</v>
       </c>
       <c r="S19" t="n">
-        <v>14000</v>
+        <v>-790000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>대한광통신, 미국 광통신주 강세에 따른 동반 상승 기대. 공매도 수량 부족 언급 및 추세 변함없음 주장.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광케이블', '공매도', '실적주']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>우리기술</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13410</v>
+        <v>17800</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.45%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.48</v>
+        <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>106</v>
+        <v>207</v>
       </c>
       <c r="F20" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="G20" t="n">
-        <v>621</v>
+        <v>900</v>
       </c>
       <c r="H20" t="n">
-        <v>5.02</v>
+        <v>6.22</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -2251,91 +2251,91 @@
         </is>
       </c>
       <c r="J20" t="n">
-        <v>13400</v>
+        <v>17720</v>
       </c>
       <c r="K20" t="n">
-        <v>13630</v>
+        <v>18230</v>
       </c>
       <c r="L20" t="n">
-        <v>13800</v>
+        <v>18750</v>
       </c>
       <c r="M20" t="n">
-        <v>13180</v>
+        <v>17500</v>
       </c>
       <c r="N20" t="n">
-        <v>5.5</v>
+        <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>70375345955</v>
+        <v>175465563060</v>
       </c>
       <c r="P20" t="n">
-        <v>30200</v>
+        <v>31500</v>
       </c>
       <c r="Q20" t="n">
-        <v>3540</v>
+        <v>1272</v>
       </c>
       <c r="R20" t="n">
-        <v>-173000</v>
+        <v>-475000</v>
       </c>
       <c r="S20" t="n">
-        <v>21000</v>
+        <v>14000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
+          <t>대한광통신 주가 상승 기대감과 함께 실적 및 미국 시장 동향 분석.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['SMR', '웨스팅하우스', '원전']</t>
+          <t>['광케이블', '실적', '추세']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>032820</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>우리기술</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>10540</v>
+        <v>13410</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-0.09%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1.01</v>
+        <v>-0.48</v>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>205</v>
+        <v>642</v>
       </c>
       <c r="H21" t="n">
-        <v>9.609999999999999</v>
+        <v>5.02</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,38 +2343,38 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>10550</v>
+        <v>13400</v>
       </c>
       <c r="K21" t="n">
-        <v>10730</v>
+        <v>13630</v>
       </c>
       <c r="L21" t="n">
-        <v>11160</v>
+        <v>13800</v>
       </c>
       <c r="M21" t="n">
-        <v>10300</v>
+        <v>13180</v>
       </c>
       <c r="N21" t="n">
-        <v>8.6</v>
+        <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>152116521240</v>
+        <v>71031401935</v>
       </c>
       <c r="P21" t="n">
-        <v>11640</v>
+        <v>30200</v>
       </c>
       <c r="Q21" t="n">
-        <v>3735</v>
+        <v>3540</v>
       </c>
       <c r="R21" t="n">
-        <v>326000</v>
+        <v>-173000</v>
       </c>
       <c r="S21" t="n">
-        <v>-790000</v>
+        <v>21000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>스웨덴 SMR 4기 계약 및 웨스팅하우스 지분 투자 협상 등 긍정적 뉴스 기반. 주가 상승 기대감 및 추가 매수 권유.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
@@ -2383,11 +2383,11 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '웨스팅하우스', '원전']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>032820</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>8450</v>
+        <v>8470</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-0.82%</t>
+          <t>'-0.59%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F22" t="n">
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>424</v>
+        <v>434</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>22468855745</v>
+        <v>23105747835</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,7 +2466,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>주가 상승 기대와 함께 기관 순매수 및 ADR 계산 언급. 회사 실적 및 재무 구조에 대한 부정적 시각도 존재.</t>
+          <t>LG디스플레이 주가 상승 기대감과 함께 회사의 재무 상태 및 경쟁력에 대한 논의.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,7 +2475,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['기관', 'ADR', '재무']</t>
+          <t>['주가', '재무', '경쟁력']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1847000</v>
+        <v>1841000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.12%</t>
+          <t>'-1.45%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="G23" t="n">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>5190243222500</v>
+        <v>5322357161000</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>주가 하락에 대한 불만과 연기금, 레버리지에 대한 비판. 향후 폭락 가능성 언급.</t>
+          <t>SK하이닉스 주가 하락에 대한 불만과 연기금, 레버리지의 영향에 대한 부정적 언급.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['하락', '연기금', '레버리지']</t>
+          <t>['주가', '하락', '연기금']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24100</v>
+        <v>24050</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.55%</t>
+          <t>'-4.75%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F24" t="n">
         <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>111139890450</v>
+        <v>111932920375</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2683,24 +2683,24 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10200</v>
+        <v>10195</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.78%</t>
+          <t>'-7.82%</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" t="n">
         <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>42501705055</v>
+        <v>42997359125</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3725</v>
+        <v>3735</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-8.14%</t>
+          <t>'-7.89%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="F26" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" t="n">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2818,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>14169923735</v>
+        <v>14390534645</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>

--- a/data/trending_integrated_20260922_15.xlsx
+++ b/data/trending_integrated_20260922_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G2" t="n">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>52617034890</v>
+        <v>52638908390</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -676,7 +676,7 @@
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5481667649</v>
+        <v>5486482714</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>65900</v>
+        <v>65600</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+26.00%</t>
+          <t>'+25.43%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F4" t="n">
         <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>183021761250</v>
+        <v>185380671650</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13480</v>
+        <v>13540</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+21.22%</t>
+          <t>'+21.76%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="F5" t="n">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G5" t="n">
-        <v>621</v>
+        <v>645</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>283953020475</v>
+        <v>284951108035</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼미금속의 단기 급등 후 변동성 및 투자자 간의 의견 대립.</t>
+          <t>역대급 거래량 동반 상승 기대감. 단기적 지수 영향 및 개인 매수세에 대한 의구심 제기.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '변동성', '주주']</t>
+          <t>['거래량', '상승 기대']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -946,7 +946,7 @@
         <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" t="n">
         <v>60</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>321165327200</v>
+        <v>322185235800</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23600</v>
+        <v>23450</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+9.77%</t>
+          <t>'+9.07%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="G7" t="n">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="H7" t="n">
         <v>1.2</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>107572549725</v>
+        <v>108411801775</v>
       </c>
       <c r="P7" t="n">
         <v>24100</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스의 임상 3상 투자 및 바이오 의약품 시장 동향과 연계된 기대감.</t>
+          <t>머크사의 임상 3상 투자 소식 및 모더나 주가 상승에 따른 기대감. 외국인 및 기타법인 매수세 유입 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상 3상', '바이오', '신고가']</t>
+          <t>['임상 3상', '외국인 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>31350</v>
+        <v>31400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+8.67%</t>
+          <t>'+8.84%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="n">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="H8" t="n">
-        <v>52.76</v>
+        <v>52.7</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>203726382725</v>
+        <v>208768312125</v>
       </c>
       <c r="P8" t="n">
         <v>31400</v>
@@ -1222,7 +1222,7 @@
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F9" t="n">
         <v>86</v>
@@ -1254,7 +1254,7 @@
         <v>11.92</v>
       </c>
       <c r="O9" t="n">
-        <v>283246655725</v>
+        <v>284672574125</v>
       </c>
       <c r="P9" t="n">
         <v>75900</v>
@@ -1303,24 +1303,24 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18770</v>
+        <v>18800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F10" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G10" t="n">
-        <v>817</v>
+        <v>834</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>163198725870</v>
+        <v>163768516270</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1406,13 +1406,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F11" t="n">
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>23887455180</v>
+        <v>23959452840</v>
       </c>
       <c r="P11" t="n">
         <v>19380</v>
@@ -1504,7 +1504,7 @@
         <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0.19</v>
       </c>
       <c r="O12" t="n">
-        <v>69813403360</v>
+        <v>69922329060</v>
       </c>
       <c r="P12" t="n">
         <v>13140</v>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6420</v>
+        <v>6430</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+1.74%</t>
+          <t>'+1.90%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>-0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="H13" t="n">
         <v>4.86</v>
@@ -1622,7 +1622,7 @@
         <v>4.95</v>
       </c>
       <c r="O13" t="n">
-        <v>55534013060</v>
+        <v>55683902790</v>
       </c>
       <c r="P13" t="n">
         <v>11760</v>
@@ -1688,7 +1688,7 @@
         <v>60</v>
       </c>
       <c r="G14" t="n">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="H14" t="n">
         <v>75.5</v>
@@ -1714,7 +1714,7 @@
         <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>1008513451000</v>
+        <v>1051155023500</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86400</v>
+        <v>86500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.41%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="F15" t="n">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="G15" t="n">
-        <v>1635</v>
+        <v>1665</v>
       </c>
       <c r="H15" t="n">
         <v>23.05</v>
@@ -1806,7 +1806,7 @@
         <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>239382549100</v>
+        <v>244811289100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>두산에너빌리티의 미국 투자 확정 및 SMR 추진 관련 긍정적 전망과 공매도 관련 부정적 언급.</t>
+          <t>미국 SMR 및 가스발전 공급 계약 체결 확정. 대미 투자 관련 긍정적 전망 및 공매도 세력 비판.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '미국 투자', '공매도']</t>
+          <t>['SMR', '공급 계약', '대미 투자']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1851,31 +1851,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>277500</v>
+        <v>321500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+1.28%</t>
+          <t>'+0.94%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>-0.4</v>
       </c>
       <c r="E16" t="n">
-        <v>800</v>
+        <v>150</v>
       </c>
       <c r="F16" t="n">
-        <v>478</v>
+        <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>1938</v>
+        <v>343</v>
       </c>
       <c r="H16" t="n">
-        <v>46.56</v>
+        <v>3.22</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>274000</v>
+        <v>318500</v>
       </c>
       <c r="K16" t="n">
-        <v>283000</v>
+        <v>333000</v>
       </c>
       <c r="L16" t="n">
-        <v>283500</v>
+        <v>349500</v>
       </c>
       <c r="M16" t="n">
-        <v>274500</v>
+        <v>319000</v>
       </c>
       <c r="N16" t="n">
-        <v>46.46</v>
+        <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>4366135550250</v>
+        <v>133470986500</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>635000</v>
       </c>
       <c r="Q16" t="n">
-        <v>81100</v>
+        <v>52600</v>
       </c>
       <c r="R16" t="n">
-        <v>749000</v>
+        <v>-8000</v>
       </c>
       <c r="S16" t="n">
-        <v>262000</v>
+        <v>8000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>정치적 언급과 함께 삼성전자 주가 반등 및 배당 관련 논쟁.</t>
+          <t>가온전선의 52주 신고가 돌파 및 텍사스 발전 프로젝트 관련 긍정적 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['배당', '정치', '주가']</t>
+          <t>['신고가', '구리', '프로젝트']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13660</v>
+        <v>276500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+0.89%</t>
+          <t>'+0.91%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.34</v>
+        <v>0.1</v>
       </c>
       <c r="E17" t="n">
-        <v>90</v>
+        <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>48</v>
+        <v>482</v>
       </c>
       <c r="G17" t="n">
-        <v>235</v>
+        <v>1967</v>
       </c>
       <c r="H17" t="n">
-        <v>3.34</v>
+        <v>46.56</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,91 +1975,91 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>13540</v>
+        <v>274000</v>
       </c>
       <c r="K17" t="n">
-        <v>13870</v>
+        <v>283000</v>
       </c>
       <c r="L17" t="n">
-        <v>14650</v>
+        <v>283500</v>
       </c>
       <c r="M17" t="n">
-        <v>13570</v>
+        <v>274500</v>
       </c>
       <c r="N17" t="n">
-        <v>3.68</v>
+        <v>46.46</v>
       </c>
       <c r="O17" t="n">
-        <v>101319925950</v>
+        <v>4702602040750</v>
       </c>
       <c r="P17" t="n">
-        <v>20300</v>
+        <v>374500</v>
       </c>
       <c r="Q17" t="n">
-        <v>2885</v>
+        <v>81100</v>
       </c>
       <c r="R17" t="n">
-        <v>2000</v>
+        <v>749000</v>
       </c>
       <c r="S17" t="n">
-        <v>16000</v>
+        <v>262000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>시장 대비 부진한 흐름과 정치적 이슈 언급. 3분기 배당 및 특별배당 기준일 혼동에 대한 지적.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['배당']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>321000</v>
+        <v>13660</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.78%</t>
+          <t>'+0.89%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="E18" t="n">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="F18" t="n">
-        <v>83</v>
+        <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>339</v>
+        <v>248</v>
       </c>
       <c r="H18" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -2067,47 +2067,47 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>318500</v>
+        <v>13540</v>
       </c>
       <c r="K18" t="n">
-        <v>333000</v>
+        <v>13870</v>
       </c>
       <c r="L18" t="n">
-        <v>349500</v>
+        <v>14650</v>
       </c>
       <c r="M18" t="n">
-        <v>319000</v>
+        <v>13570</v>
       </c>
       <c r="N18" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>132418395500</v>
+        <v>101775118130</v>
       </c>
       <c r="P18" t="n">
-        <v>635000</v>
+        <v>20300</v>
       </c>
       <c r="Q18" t="n">
-        <v>52600</v>
+        <v>2885</v>
       </c>
       <c r="R18" t="n">
-        <v>-8000</v>
+        <v>2000</v>
       </c>
       <c r="S18" t="n">
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>가온전선의 52주 신고가 돌파 및 텍사스 발전 프로젝트 관련 긍정적 전망.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['신고가', '구리', '프로젝트']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X18" t="n">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
@@ -2131,11 +2131,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>10610</v>
+        <v>10620</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.57%</t>
+          <t>'+0.66%</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2148,7 +2148,7 @@
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="H19" t="n">
         <v>9.609999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>153589043530</v>
+        <v>154480008430</v>
       </c>
       <c r="P19" t="n">
         <v>11640</v>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17800</v>
+        <v>17810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.45%</t>
+          <t>'+0.51%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F20" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G20" t="n">
-        <v>900</v>
+        <v>933</v>
       </c>
       <c r="H20" t="n">
         <v>6.22</v>
@@ -2266,7 +2266,7 @@
         <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>175465563060</v>
+        <v>176344664660</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13410</v>
+        <v>13420</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.07%</t>
+          <t>'+0.15%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.48</v>
       </c>
       <c r="E21" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F21" t="n">
         <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>642</v>
+        <v>652</v>
       </c>
       <c r="H21" t="n">
         <v>5.02</v>
@@ -2358,7 +2358,7 @@
         <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>71031401935</v>
+        <v>71344114775</v>
       </c>
       <c r="P21" t="n">
         <v>30200</v>
@@ -2424,7 +2424,7 @@
         <v>54</v>
       </c>
       <c r="G22" t="n">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>23105747835</v>
+        <v>24071869915</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2499,11 +2499,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1841000</v>
+        <v>1840000</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-1.45%</t>
+          <t>'-1.50%</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G23" t="n">
-        <v>1456</v>
+        <v>1558</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>5322357161000</v>
+        <v>5642905401000</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>SK하이닉스 주가 하락에 대한 불만과 연기금, 레버리지의 영향에 대한 부정적 언급.</t>
+          <t>단기 상승 후 하락 가능성 및 연기금, 레버리지 영향에 대한 부정적 전망. 공매도 및 외인 동향 주시.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['주가', '하락', '연기금']</t>
+          <t>['공매도', '연기금']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24050</v>
+        <v>23950</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-5.15%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>111932920375</v>
+        <v>112531191375</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2683,11 +2683,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>10195</v>
+        <v>10200</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>'-7.82%</t>
+          <t>'-7.78%</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2700,7 +2700,7 @@
         <v>64</v>
       </c>
       <c r="G25" t="n">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>42997359125</v>
+        <v>43144789925</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2775,24 +2775,24 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3735</v>
+        <v>3725</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>'-7.89%</t>
+          <t>'-8.14%</t>
         </is>
       </c>
       <c r="D26" t="n">
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>143</v>
+        <v>151</v>
       </c>
       <c r="F26" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G26" t="n">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2818,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>14390534645</v>
+        <v>14594694445</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>

--- a/data/trending_integrated_20260922_15.xlsx
+++ b/data/trending_integrated_20260922_15.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G2" t="n">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>493</v>
+        <v>498</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5486482714</v>
+        <v>5486491369</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -768,7 +768,7 @@
         <v>76</v>
       </c>
       <c r="G4" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>185380671650</v>
+        <v>185395825250</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>브로드컴 투자 공급 계약 관련 호재와 함께 급등 기대감. 단기 고점 매도 의견도 일부 존재.</t>
+          <t>코리아써키트, 브로드컴 투자 공급 계약으로 인한 급등세. 6만원 위 매도 기회 및 30만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['브로드컴', '공급 계약', '급등']</t>
+          <t>['브로드컴', '공급계약', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -854,13 +854,13 @@
         <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F5" t="n">
         <v>121</v>
       </c>
       <c r="G5" t="n">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="H5" t="n">
         <v>0.62</v>
@@ -886,7 +886,7 @@
         <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>284951108035</v>
+        <v>285008477015</v>
       </c>
       <c r="P5" t="n">
         <v>20850</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>역대급 거래량 동반 상승 기대감. 단기적 지수 영향 및 개인 매수세에 대한 의구심 제기.</t>
+          <t>삼미금속, 역대급 거래량 동반 상승 기대감. 13600원 돌파 및 길게 보고 크게 먹는 타임 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['거래량', '상승 기대']</t>
+          <t>['거래량', '대장주', '월봉']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -952,7 +952,7 @@
         <v>60</v>
       </c>
       <c r="G6" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
         <v>18.2</v>
@@ -978,7 +978,7 @@
         <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>322185235800</v>
+        <v>322215893700</v>
       </c>
       <c r="P6" t="n">
         <v>198000</v>
@@ -1038,13 +1038,13 @@
         <v>-0.05</v>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="F7" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G7" t="n">
-        <v>336</v>
+        <v>357</v>
       </c>
       <c r="H7" t="n">
         <v>1.2</v>
@@ -1070,7 +1070,7 @@
         <v>1.25</v>
       </c>
       <c r="O7" t="n">
-        <v>108411801775</v>
+        <v>108428849925</v>
       </c>
       <c r="P7" t="n">
         <v>24100</v>
@@ -1086,16 +1086,16 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 소식 및 모더나 주가 상승에 따른 기대감. 외국인 및 기타법인 매수세 유입 관찰.</t>
+          <t>인제니아테라퓨틱스, 머크의 임상 3상 투자 소식에 대한 기대감. 15000원 이하 상장 감사 및 10만 목표가 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수']</t>
+          <t>['임상3상', '머크', '텐버거']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1133,10 +1133,10 @@
         <v>115</v>
       </c>
       <c r="F8" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G8" t="n">
-        <v>494</v>
+        <v>499</v>
       </c>
       <c r="H8" t="n">
         <v>52.7</v>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>208768312125</v>
+        <v>208878055125</v>
       </c>
       <c r="P8" t="n">
         <v>31400</v>
@@ -1222,13 +1222,13 @@
         <v>-0.62</v>
       </c>
       <c r="E9" t="n">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G9" t="n">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="H9" t="n">
         <v>11.3</v>
@@ -1254,7 +1254,7 @@
         <v>11.92</v>
       </c>
       <c r="O9" t="n">
-        <v>284672574125</v>
+        <v>284857307725</v>
       </c>
       <c r="P9" t="n">
         <v>75900</v>
@@ -1270,16 +1270,16 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>단기 목표가 3만5천원 언급 및 20% 상승 예상. AI 전력 수요 증가 관련주로 주목받으나, 700원 저항선 돌파 실패 및 주가 변동성에 대한 우려도 존재.</t>
+          <t>대한전선, 6.5원 물린 투자자들의 아쉬움 속 20% 상승 기대감 존재. AI 전력 수요 증가는 긍정적 요소.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['AI', '전력', '상승']</t>
+          <t>['AI 전력', '거래량', '전고점']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1314,13 +1314,13 @@
         <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F10" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" t="n">
-        <v>834</v>
+        <v>857</v>
       </c>
       <c r="H10" t="n">
         <v>10.47</v>
@@ -1346,7 +1346,7 @@
         <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>163768516270</v>
+        <v>163780473070</v>
       </c>
       <c r="P10" t="n">
         <v>40350</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>감사원 신고 및 공매도 관련 의혹 제기로 주가 부양 기대감 형성. 뉴스 언급.</t>
+          <t>대우건설, 공매도 세력과의 전쟁 선포. 감사원 신고 및 공매도 구조 관련 내용 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', '감사원', '뉴스']</t>
+          <t>['공매도', '시세조종', '감사원']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1412,7 +1412,7 @@
         <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>23959452840</v>
+        <v>23963276310</v>
       </c>
       <c r="P11" t="n">
         <v>19380</v>
@@ -1498,13 +1498,13 @@
         <v>-0.19</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F12" t="n">
         <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0.19</v>
       </c>
       <c r="O12" t="n">
-        <v>69922329060</v>
+        <v>69939061100</v>
       </c>
       <c r="P12" t="n">
         <v>13140</v>
@@ -1590,13 +1590,13 @@
         <v>-0.09</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F13" t="n">
         <v>48</v>
       </c>
       <c r="G13" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="H13" t="n">
         <v>4.86</v>
@@ -1622,7 +1622,7 @@
         <v>4.95</v>
       </c>
       <c r="O13" t="n">
-        <v>55683902790</v>
+        <v>55691998160</v>
       </c>
       <c r="P13" t="n">
         <v>11760</v>
@@ -1682,13 +1682,13 @@
         <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" t="n">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="H14" t="n">
         <v>75.5</v>
@@ -1714,7 +1714,7 @@
         <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>1051155023500</v>
+        <v>1051758433000</v>
       </c>
       <c r="P14" t="n">
         <v>243500</v>
@@ -1774,13 +1774,13 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="F15" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G15" t="n">
-        <v>1665</v>
+        <v>1712</v>
       </c>
       <c r="H15" t="n">
         <v>23.05</v>
@@ -1806,7 +1806,7 @@
         <v>23.12</v>
       </c>
       <c r="O15" t="n">
-        <v>244811289100</v>
+        <v>244819074100</v>
       </c>
       <c r="P15" t="n">
         <v>139200</v>
@@ -1822,16 +1822,16 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 SMR 및 가스발전 공급 계약 체결 확정. 대미 투자 관련 긍정적 전망 및 공매도 세력 비판.</t>
+          <t>두산에너빌리티, 대미 투자 SMR 추진 확정 소식에 대한 기대감 상승. 가스터빈 공급 계약 체결.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', '대미 투자']</t>
+          <t>['SMR', '대미투자', '가스터빈']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1872,7 +1872,7 @@
         <v>83</v>
       </c>
       <c r="G16" t="n">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="H16" t="n">
         <v>3.22</v>
@@ -1898,7 +1898,7 @@
         <v>3.62</v>
       </c>
       <c r="O16" t="n">
-        <v>133470986500</v>
+        <v>133471629500</v>
       </c>
       <c r="P16" t="n">
         <v>635000</v>
@@ -1961,10 +1961,10 @@
         <v>800</v>
       </c>
       <c r="F17" t="n">
-        <v>482</v>
+        <v>487</v>
       </c>
       <c r="G17" t="n">
-        <v>1967</v>
+        <v>1980</v>
       </c>
       <c r="H17" t="n">
         <v>46.56</v>
@@ -1990,7 +1990,7 @@
         <v>46.46</v>
       </c>
       <c r="O17" t="n">
-        <v>4702602040750</v>
+        <v>4704974134250</v>
       </c>
       <c r="P17" t="n">
         <v>374500</v>
@@ -2006,7 +2006,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>시장 대비 부진한 흐름과 정치적 이슈 언급. 3분기 배당 및 특별배당 기준일 혼동에 대한 지적.</t>
+          <t>삼성전자, 미국 증시 대비 처참한 성적 기록. 정치 관련 언급과 함께 30만원 기대감이 혼재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['배당']</t>
+          <t>['공매도', '미국증시', '배당']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2056,7 +2056,7 @@
         <v>49</v>
       </c>
       <c r="G18" t="n">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="H18" t="n">
         <v>3.34</v>
@@ -2082,7 +2082,7 @@
         <v>3.68</v>
       </c>
       <c r="O18" t="n">
-        <v>101775118130</v>
+        <v>101787494090</v>
       </c>
       <c r="P18" t="n">
         <v>20300</v>
@@ -2148,7 +2148,7 @@
         <v>42</v>
       </c>
       <c r="G19" t="n">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="H19" t="n">
         <v>9.609999999999999</v>
@@ -2174,7 +2174,7 @@
         <v>8.6</v>
       </c>
       <c r="O19" t="n">
-        <v>154480008430</v>
+        <v>154511772850</v>
       </c>
       <c r="P19" t="n">
         <v>11640</v>
@@ -2234,13 +2234,13 @@
         <v>-1.68</v>
       </c>
       <c r="E20" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F20" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G20" t="n">
-        <v>933</v>
+        <v>963</v>
       </c>
       <c r="H20" t="n">
         <v>6.22</v>
@@ -2266,7 +2266,7 @@
         <v>7.9</v>
       </c>
       <c r="O20" t="n">
-        <v>176344664660</v>
+        <v>176428229180</v>
       </c>
       <c r="P20" t="n">
         <v>31500</v>
@@ -2326,13 +2326,13 @@
         <v>-0.48</v>
       </c>
       <c r="E21" t="n">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G21" t="n">
-        <v>652</v>
+        <v>657</v>
       </c>
       <c r="H21" t="n">
         <v>5.02</v>
@@ -2358,7 +2358,7 @@
         <v>5.5</v>
       </c>
       <c r="O21" t="n">
-        <v>71344114775</v>
+        <v>71349912215</v>
       </c>
       <c r="P21" t="n">
         <v>30200</v>
@@ -2418,13 +2418,13 @@
         <v>0.01</v>
       </c>
       <c r="E22" t="n">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F22" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G22" t="n">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="H22" t="n">
         <v>26.58</v>
@@ -2450,7 +2450,7 @@
         <v>26.57</v>
       </c>
       <c r="O22" t="n">
-        <v>24071869915</v>
+        <v>24071954615</v>
       </c>
       <c r="P22" t="n">
         <v>17950</v>
@@ -2466,16 +2466,16 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>LG디스플레이 주가 상승 기대감과 함께 회사의 재무 상태 및 경쟁력에 대한 논의.</t>
+          <t>LG디스플레이, 주가 부진에 대한 불만과 함께 10500원 돌파 및 LG전자와 같은 신고점 행진 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['주가', '재무', '경쟁력']</t>
+          <t>['반도체', '주가부진', '인터포저']</t>
         </is>
       </c>
       <c r="X22" t="n">
@@ -2513,10 +2513,10 @@
         <v>800</v>
       </c>
       <c r="F23" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G23" t="n">
-        <v>1558</v>
+        <v>1650</v>
       </c>
       <c r="H23" t="n">
         <v>50.17</v>
@@ -2542,7 +2542,7 @@
         <v>50.23</v>
       </c>
       <c r="O23" t="n">
-        <v>5642905401000</v>
+        <v>5643479481000</v>
       </c>
       <c r="P23" t="n">
         <v>2987000</v>
@@ -2558,16 +2558,16 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>단기 상승 후 하락 가능성 및 연기금, 레버리지 영향에 대한 부정적 전망. 공매도 및 외인 동향 주시.</t>
+          <t>SK하이닉스, 연기금 및 외인 매매에 대한 불만 고조. 200만원 재도전 가능성 있으나 하락 추세 우려.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['공매도', '연기금']</t>
+          <t>['연기금', '외인매매', '동시호가']</t>
         </is>
       </c>
       <c r="X23" t="n">
@@ -2602,13 +2602,13 @@
         <v>1.41</v>
       </c>
       <c r="E24" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F24" t="n">
         <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="H24" t="n">
         <v>1.76</v>
@@ -2634,7 +2634,7 @@
         <v>0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>112531191375</v>
+        <v>112581438475</v>
       </c>
       <c r="P24" t="n">
         <v>39350</v>
@@ -2694,13 +2694,13 @@
         <v>-0.4</v>
       </c>
       <c r="E25" t="n">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="G25" t="n">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="H25" t="n">
         <v>17.89</v>
@@ -2726,7 +2726,7 @@
         <v>18.29</v>
       </c>
       <c r="O25" t="n">
-        <v>43144789925</v>
+        <v>43153072325</v>
       </c>
       <c r="P25" t="n">
         <v>22450</v>
@@ -2786,13 +2786,13 @@
         <v>0.63</v>
       </c>
       <c r="E26" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F26" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G26" t="n">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="H26" t="n">
         <v>0.96</v>
@@ -2818,7 +2818,7 @@
         <v>0.33</v>
       </c>
       <c r="O26" t="n">
-        <v>14594694445</v>
+        <v>14599015445</v>
       </c>
       <c r="P26" t="n">
         <v>6480</v>
